--- a/Results/Phase 2/Methanol/methanol ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Methanol/methanol ecotoxicity freshwater results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.98812083642417</v>
+        <v>14.61464250880036</v>
       </c>
       <c r="C33" t="n">
-        <v>8.682343764562022</v>
+        <v>8.488421551705425</v>
       </c>
       <c r="D33" t="n">
-        <v>14.85106407565044</v>
+        <v>14.51206034670018</v>
       </c>
       <c r="E33" t="n">
-        <v>11.94024634123866</v>
+        <v>11.80476245262453</v>
       </c>
       <c r="F33" t="n">
-        <v>15.04035004214991</v>
+        <v>14.61642723665182</v>
       </c>
       <c r="G33" t="n">
-        <v>17.55718110487044</v>
+        <v>16.16629900001969</v>
       </c>
       <c r="H33" t="n">
-        <v>14.57530949813635</v>
+        <v>14.34608393712984</v>
       </c>
       <c r="I33" t="n">
-        <v>14.97065786005263</v>
+        <v>14.57930323308838</v>
       </c>
       <c r="J33" t="n">
-        <v>16.13478251598859</v>
+        <v>15.29212681378137</v>
       </c>
       <c r="K33" t="n">
-        <v>14.91938128236617</v>
+        <v>14.55337325951074</v>
       </c>
       <c r="L33" t="n">
-        <v>14.78541841851875</v>
+        <v>14.48287826160762</v>
       </c>
       <c r="M33" t="n">
-        <v>19.23801765020104</v>
+        <v>17.04995697678558</v>
       </c>
       <c r="N33" t="n">
-        <v>14.84672588242222</v>
+        <v>14.51432155341815</v>
       </c>
       <c r="O33" t="n">
-        <v>22.90460223928155</v>
+        <v>22.43491314365816</v>
       </c>
       <c r="P33" t="n">
-        <v>15.59709391247746</v>
+        <v>14.98428932145285</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.65120449591738</v>
+        <v>14.39796010765982</v>
       </c>
       <c r="R33" t="n">
-        <v>14.58272508329614</v>
+        <v>14.3530912682663</v>
       </c>
       <c r="S33" t="n">
-        <v>15.3565021581707</v>
+        <v>14.83251289884212</v>
       </c>
       <c r="T33" t="n">
-        <v>14.69784647507173</v>
+        <v>14.42232739192712</v>
       </c>
       <c r="U33" t="n">
-        <v>19.59728846768554</v>
+        <v>18.86163439221747</v>
       </c>
       <c r="V33" t="n">
-        <v>14.92104888055757</v>
+        <v>14.57072493554029</v>
       </c>
       <c r="W33" t="n">
-        <v>21.26301015546262</v>
+        <v>20.7180600596682</v>
       </c>
       <c r="X33" t="n">
-        <v>15.03807528380259</v>
+        <v>14.62316322113983</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.4581597764681</v>
+        <v>14.87920614130594</v>
       </c>
       <c r="Z33" t="n">
-        <v>21.98314345439079</v>
+        <v>21.47861576525171</v>
       </c>
       <c r="AA33" t="n">
-        <v>15.54631195633915</v>
+        <v>14.93070908766413</v>
       </c>
       <c r="AB33" t="n">
-        <v>19.30680248847641</v>
+        <v>17.05179269225639</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.27196824267765</v>
+        <v>14.04358205611879</v>
       </c>
       <c r="C33" t="n">
-        <v>8.16962886082044</v>
+        <v>8.040499891485366</v>
       </c>
       <c r="D33" t="n">
-        <v>14.04436620107771</v>
+        <v>13.89535360370025</v>
       </c>
       <c r="E33" t="n">
-        <v>11.45421752735792</v>
+        <v>11.39589879999578</v>
       </c>
       <c r="F33" t="n">
-        <v>14.08594184311308</v>
+        <v>13.92012906640732</v>
       </c>
       <c r="G33" t="n">
-        <v>14.22477954141719</v>
+        <v>14.01271738190889</v>
       </c>
       <c r="H33" t="n">
-        <v>14.22372934943426</v>
+        <v>13.99725200122959</v>
       </c>
       <c r="I33" t="n">
-        <v>14.3272065809656</v>
+        <v>14.0620194046514</v>
       </c>
       <c r="J33" t="n">
-        <v>14.2009594474628</v>
+        <v>13.99452303019299</v>
       </c>
       <c r="K33" t="n">
-        <v>14.25805919630599</v>
+        <v>14.02435768959966</v>
       </c>
       <c r="L33" t="n">
-        <v>14.15935910600168</v>
+        <v>13.96882574601735</v>
       </c>
       <c r="M33" t="n">
-        <v>14.17585745713051</v>
+        <v>13.97144045327756</v>
       </c>
       <c r="N33" t="n">
-        <v>14.14456620257603</v>
+        <v>13.95880378925472</v>
       </c>
       <c r="O33" t="n">
-        <v>21.24249078383342</v>
+        <v>21.05361398841722</v>
       </c>
       <c r="P33" t="n">
-        <v>14.20637626452291</v>
+        <v>14.00387817631163</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.22025157539627</v>
+        <v>14.00503758782443</v>
       </c>
       <c r="R33" t="n">
-        <v>14.28263950237275</v>
+        <v>14.03401416617906</v>
       </c>
       <c r="S33" t="n">
-        <v>14.17887047490586</v>
+        <v>13.98529233547658</v>
       </c>
       <c r="T33" t="n">
-        <v>14.05706984789007</v>
+        <v>13.90471943241147</v>
       </c>
       <c r="U33" t="n">
-        <v>17.72819857908868</v>
+        <v>17.50607666350843</v>
       </c>
       <c r="V33" t="n">
-        <v>14.19025505976784</v>
+        <v>13.99051145977319</v>
       </c>
       <c r="W33" t="n">
-        <v>20.13828680806442</v>
+        <v>19.79884032768899</v>
       </c>
       <c r="X33" t="n">
-        <v>14.85644363699915</v>
+        <v>14.38511920812022</v>
       </c>
       <c r="Y33" t="n">
-        <v>14.78274230394603</v>
+        <v>14.33676476825458</v>
       </c>
       <c r="Z33" t="n">
-        <v>20.5786628141948</v>
+        <v>20.41299750716431</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.35907834269042</v>
+        <v>14.08720950709335</v>
       </c>
       <c r="AB33" t="n">
-        <v>14.10344117603605</v>
+        <v>13.92781745931157</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.95205748695312</v>
+        <v>14.58169025388767</v>
       </c>
       <c r="C33" t="n">
-        <v>8.50803680477418</v>
+        <v>8.368878840423749</v>
       </c>
       <c r="D33" t="n">
-        <v>15.10584639467501</v>
+        <v>14.64783017879222</v>
       </c>
       <c r="E33" t="n">
-        <v>11.8813629435092</v>
+        <v>11.76119117891894</v>
       </c>
       <c r="F33" t="n">
-        <v>14.91665907371408</v>
+        <v>14.53490916203992</v>
       </c>
       <c r="G33" t="n">
-        <v>17.41618441865207</v>
+        <v>16.07544528386061</v>
       </c>
       <c r="H33" t="n">
-        <v>14.38570504656778</v>
+        <v>14.22449629171105</v>
       </c>
       <c r="I33" t="n">
-        <v>14.61229266684341</v>
+        <v>14.35909015951638</v>
       </c>
       <c r="J33" t="n">
-        <v>16.14838904159876</v>
+        <v>15.28930500979693</v>
       </c>
       <c r="K33" t="n">
-        <v>14.88311659124797</v>
+        <v>14.52384492692213</v>
       </c>
       <c r="L33" t="n">
-        <v>14.66542676147739</v>
+        <v>14.39932245355838</v>
       </c>
       <c r="M33" t="n">
-        <v>18.86163556426061</v>
+        <v>16.82468083621903</v>
       </c>
       <c r="N33" t="n">
-        <v>14.74929954402988</v>
+        <v>14.44464891851253</v>
       </c>
       <c r="O33" t="n">
-        <v>22.73145449746564</v>
+        <v>22.29292808580529</v>
       </c>
       <c r="P33" t="n">
-        <v>15.83347576689524</v>
+        <v>15.11703710517611</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.6544034221891</v>
+        <v>14.38776347581054</v>
       </c>
       <c r="R33" t="n">
-        <v>14.44271289728281</v>
+        <v>14.25971084512464</v>
       </c>
       <c r="S33" t="n">
-        <v>15.30873687674055</v>
+        <v>14.79371200220281</v>
       </c>
       <c r="T33" t="n">
-        <v>14.61346129815029</v>
+        <v>14.36071055752902</v>
       </c>
       <c r="U33" t="n">
-        <v>19.24101660930942</v>
+        <v>18.61009678565469</v>
       </c>
       <c r="V33" t="n">
-        <v>14.69726062586225</v>
+        <v>14.42317239582654</v>
       </c>
       <c r="W33" t="n">
-        <v>21.08739126306246</v>
+        <v>20.57345582409995</v>
       </c>
       <c r="X33" t="n">
-        <v>15.05554245277458</v>
+        <v>14.62164821245533</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.33661015006154</v>
+        <v>14.79678050246309</v>
       </c>
       <c r="Z33" t="n">
-        <v>21.72331113366223</v>
+        <v>21.28596667413488</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.94763744363433</v>
+        <v>14.56485454716381</v>
       </c>
       <c r="AB33" t="n">
-        <v>19.13763675960316</v>
+        <v>16.94132225381577</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.92684578560535</v>
+        <v>14.55681076789708</v>
       </c>
       <c r="C33" t="n">
-        <v>8.481793874197416</v>
+        <v>8.342402770562181</v>
       </c>
       <c r="D33" t="n">
-        <v>15.23213875475726</v>
+        <v>14.71436204882755</v>
       </c>
       <c r="E33" t="n">
-        <v>11.83471040394934</v>
+        <v>11.72628940350093</v>
       </c>
       <c r="F33" t="n">
-        <v>15.16025181490721</v>
+        <v>14.67092003846734</v>
       </c>
       <c r="G33" t="n">
-        <v>17.17823754270414</v>
+        <v>15.93287102572384</v>
       </c>
       <c r="H33" t="n">
-        <v>14.36871351267619</v>
+        <v>14.20654613785778</v>
       </c>
       <c r="I33" t="n">
-        <v>14.90133746554033</v>
+        <v>14.51833598611691</v>
       </c>
       <c r="J33" t="n">
-        <v>16.02409505498616</v>
+        <v>15.20890310907065</v>
       </c>
       <c r="K33" t="n">
-        <v>14.94223715994119</v>
+        <v>14.55539885745454</v>
       </c>
       <c r="L33" t="n">
-        <v>14.59044770604084</v>
+        <v>14.34649955195532</v>
       </c>
       <c r="M33" t="n">
-        <v>18.277316863411</v>
+        <v>16.47547241480734</v>
       </c>
       <c r="N33" t="n">
-        <v>14.61173468626959</v>
+        <v>14.35521251740137</v>
       </c>
       <c r="O33" t="n">
-        <v>22.55680793051719</v>
+        <v>22.1549363795633</v>
       </c>
       <c r="P33" t="n">
-        <v>15.77907876665134</v>
+        <v>15.07965459826895</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.69739325978935</v>
+        <v>14.40621808589456</v>
       </c>
       <c r="R33" t="n">
-        <v>14.38333479236809</v>
+        <v>14.21692454012159</v>
       </c>
       <c r="S33" t="n">
-        <v>15.20635691551151</v>
+        <v>14.72525854477067</v>
       </c>
       <c r="T33" t="n">
-        <v>14.59491221730025</v>
+        <v>14.34148725862215</v>
       </c>
       <c r="U33" t="n">
-        <v>18.46328249290401</v>
+        <v>18.11509035421028</v>
       </c>
       <c r="V33" t="n">
-        <v>14.81580374679258</v>
+        <v>14.48987191825761</v>
       </c>
       <c r="W33" t="n">
-        <v>20.88175912218241</v>
+        <v>20.42217342814008</v>
       </c>
       <c r="X33" t="n">
-        <v>15.21330021065875</v>
+        <v>14.70670471845258</v>
       </c>
       <c r="Y33" t="n">
-        <v>16.08803248144752</v>
+        <v>15.2355249670314</v>
       </c>
       <c r="Z33" t="n">
-        <v>21.67354206659551</v>
+        <v>21.25294370808097</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.75097565495312</v>
+        <v>14.43980141356751</v>
       </c>
       <c r="AB33" t="n">
-        <v>18.78760049071388</v>
+        <v>16.72880575315532</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.87333109145953</v>
+        <v>14.51745906450764</v>
       </c>
       <c r="C33" t="n">
-        <v>8.502709068620806</v>
+        <v>8.344370413140361</v>
       </c>
       <c r="D33" t="n">
-        <v>14.96117014185804</v>
+        <v>14.54954632826477</v>
       </c>
       <c r="E33" t="n">
-        <v>11.7414252351765</v>
+        <v>11.65719043613718</v>
       </c>
       <c r="F33" t="n">
-        <v>15.28980121323309</v>
+        <v>14.73812831897144</v>
       </c>
       <c r="G33" t="n">
-        <v>16.73687957930691</v>
+        <v>15.67068672094333</v>
       </c>
       <c r="H33" t="n">
-        <v>14.37598379825792</v>
+        <v>14.19995417845441</v>
       </c>
       <c r="I33" t="n">
-        <v>14.96819288546181</v>
+        <v>14.54826364906924</v>
       </c>
       <c r="J33" t="n">
-        <v>15.78579075195045</v>
+        <v>15.06298126665018</v>
       </c>
       <c r="K33" t="n">
-        <v>14.98769868612068</v>
+        <v>14.57359580328618</v>
       </c>
       <c r="L33" t="n">
-        <v>14.57526945975019</v>
+        <v>14.3273995900671</v>
       </c>
       <c r="M33" t="n">
-        <v>17.5543702909859</v>
+        <v>16.07553141726942</v>
       </c>
       <c r="N33" t="n">
-        <v>14.51272133146207</v>
+        <v>14.28634884498672</v>
       </c>
       <c r="O33" t="n">
-        <v>22.21917571026831</v>
+        <v>21.89990180909004</v>
       </c>
       <c r="P33" t="n">
-        <v>15.58927962527367</v>
+        <v>14.9626689656403</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.61563754564518</v>
+        <v>14.348877355579</v>
       </c>
       <c r="R33" t="n">
-        <v>14.63855142819657</v>
+        <v>14.3531991317206</v>
       </c>
       <c r="S33" t="n">
-        <v>15.12868008931569</v>
+        <v>14.67036740434149</v>
       </c>
       <c r="T33" t="n">
-        <v>14.6596657898425</v>
+        <v>14.36849831281812</v>
       </c>
       <c r="U33" t="n">
-        <v>18.25075606674172</v>
+        <v>17.97391179477767</v>
       </c>
       <c r="V33" t="n">
-        <v>15.02102688213657</v>
+        <v>14.60937014397339</v>
       </c>
       <c r="W33" t="n">
-        <v>20.83189833097346</v>
+        <v>20.37684591255223</v>
       </c>
       <c r="X33" t="n">
-        <v>15.23858933759532</v>
+        <v>14.71707962599405</v>
       </c>
       <c r="Y33" t="n">
-        <v>16.98081744367305</v>
+        <v>15.74537371886509</v>
       </c>
       <c r="Z33" t="n">
-        <v>21.51288262978072</v>
+        <v>21.14408483617738</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.78724594591824</v>
+        <v>14.45065410436622</v>
       </c>
       <c r="AB33" t="n">
-        <v>18.30991685065444</v>
+        <v>16.45834077318082</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.38330094049666</v>
+        <v>14.13789079939741</v>
       </c>
       <c r="C33" t="n">
-        <v>8.205595764361746</v>
+        <v>8.09046209251132</v>
       </c>
       <c r="D33" t="n">
-        <v>14.19389923372373</v>
+        <v>14.0130742432843</v>
       </c>
       <c r="E33" t="n">
-        <v>11.62989758667494</v>
+        <v>11.52859525353468</v>
       </c>
       <c r="F33" t="n">
-        <v>14.17384722980574</v>
+        <v>13.99947540122614</v>
       </c>
       <c r="G33" t="n">
-        <v>14.8578987188157</v>
+        <v>14.43601757339192</v>
       </c>
       <c r="H33" t="n">
-        <v>14.42880275849232</v>
+        <v>14.14387301380938</v>
       </c>
       <c r="I33" t="n">
-        <v>14.25068458295336</v>
+        <v>14.04524720117184</v>
       </c>
       <c r="J33" t="n">
-        <v>14.62672095384842</v>
+        <v>14.28484060855226</v>
       </c>
       <c r="K33" t="n">
-        <v>14.41716653406571</v>
+        <v>14.14675164182573</v>
       </c>
       <c r="L33" t="n">
-        <v>14.41949117808214</v>
+        <v>14.1553441382638</v>
       </c>
       <c r="M33" t="n">
-        <v>15.47131694630407</v>
+        <v>14.78054220168904</v>
       </c>
       <c r="N33" t="n">
-        <v>14.35704942207016</v>
+        <v>14.11351416554147</v>
       </c>
       <c r="O33" t="n">
-        <v>21.49875769968554</v>
+        <v>21.27328866674995</v>
       </c>
       <c r="P33" t="n">
-        <v>14.60429593519901</v>
+        <v>14.27310352168826</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.40053578139278</v>
+        <v>14.13941740529134</v>
       </c>
       <c r="R33" t="n">
-        <v>14.21140728663997</v>
+        <v>14.0215514568496</v>
       </c>
       <c r="S33" t="n">
-        <v>14.43332995435573</v>
+        <v>14.17275930254443</v>
       </c>
       <c r="T33" t="n">
-        <v>14.20922665838369</v>
+        <v>14.02041912167941</v>
       </c>
       <c r="U33" t="n">
-        <v>17.94439474016968</v>
+        <v>17.67647736057211</v>
       </c>
       <c r="V33" t="n">
-        <v>14.2361701078164</v>
+        <v>14.04423616665878</v>
       </c>
       <c r="W33" t="n">
-        <v>20.51699386088706</v>
+        <v>20.06905123123247</v>
       </c>
       <c r="X33" t="n">
-        <v>14.46127910664977</v>
+        <v>14.17155823371093</v>
       </c>
       <c r="Y33" t="n">
-        <v>14.34523097602859</v>
+        <v>14.10622576150959</v>
       </c>
       <c r="Z33" t="n">
-        <v>21.02432409963443</v>
+        <v>20.73926894225267</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.3319779563361</v>
+        <v>14.09888163451732</v>
       </c>
       <c r="AB33" t="n">
-        <v>15.22846303575201</v>
+        <v>14.6100888998807</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.27743347549442</v>
+        <v>14.04336110956913</v>
       </c>
       <c r="C33" t="n">
-        <v>8.177365266227786</v>
+        <v>8.041247211199067</v>
       </c>
       <c r="D33" t="n">
-        <v>13.99364786647934</v>
+        <v>13.86087806241825</v>
       </c>
       <c r="E33" t="n">
-        <v>11.46749779992666</v>
+        <v>11.40540732438379</v>
       </c>
       <c r="F33" t="n">
-        <v>14.07808644073942</v>
+        <v>13.9122543195833</v>
       </c>
       <c r="G33" t="n">
-        <v>14.18274310926748</v>
+        <v>13.98247154324075</v>
       </c>
       <c r="H33" t="n">
-        <v>14.26367894979552</v>
+        <v>14.01700351655456</v>
       </c>
       <c r="I33" t="n">
-        <v>14.17874501034177</v>
+        <v>13.97144955108753</v>
       </c>
       <c r="J33" t="n">
-        <v>14.18956365004851</v>
+        <v>13.98496533719842</v>
       </c>
       <c r="K33" t="n">
-        <v>14.1685334733798</v>
+        <v>13.96603186251916</v>
       </c>
       <c r="L33" t="n">
-        <v>14.10306413655865</v>
+        <v>13.9269261015553</v>
       </c>
       <c r="M33" t="n">
-        <v>14.09206319663992</v>
+        <v>13.91448199480264</v>
       </c>
       <c r="N33" t="n">
-        <v>14.20861509715745</v>
+        <v>13.99531583940427</v>
       </c>
       <c r="O33" t="n">
-        <v>21.45222747079475</v>
+        <v>21.18921841789356</v>
       </c>
       <c r="P33" t="n">
-        <v>14.18982695947734</v>
+        <v>13.99054534165579</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.2181131147497</v>
+        <v>14.00303163775834</v>
       </c>
       <c r="R33" t="n">
-        <v>14.13894851160418</v>
+        <v>13.94702107249918</v>
       </c>
       <c r="S33" t="n">
-        <v>14.16600460448857</v>
+        <v>13.97512876484647</v>
       </c>
       <c r="T33" t="n">
-        <v>14.02012096392799</v>
+        <v>13.87623363167097</v>
       </c>
       <c r="U33" t="n">
-        <v>17.59497442159019</v>
+        <v>17.40385696801691</v>
       </c>
       <c r="V33" t="n">
-        <v>14.21405453333878</v>
+        <v>14.00212966239252</v>
       </c>
       <c r="W33" t="n">
-        <v>20.02698831389717</v>
+        <v>19.71426851963007</v>
       </c>
       <c r="X33" t="n">
-        <v>14.78658010160355</v>
+        <v>14.34159874626551</v>
       </c>
       <c r="Y33" t="n">
-        <v>14.43208044450105</v>
+        <v>14.12709903858157</v>
       </c>
       <c r="Z33" t="n">
-        <v>20.71859506143526</v>
+        <v>20.5037892719378</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.24030717329232</v>
+        <v>14.01377567616472</v>
       </c>
       <c r="AB33" t="n">
-        <v>14.07059194581382</v>
+        <v>13.90553552866801</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.14904331335961</v>
+        <v>13.95820580895006</v>
       </c>
       <c r="C33" t="n">
-        <v>8.120591523203897</v>
+        <v>8.000726510949539</v>
       </c>
       <c r="D33" t="n">
-        <v>14.01792791945777</v>
+        <v>13.86981534574314</v>
       </c>
       <c r="E33" t="n">
-        <v>11.48500462406358</v>
+        <v>11.40839576180477</v>
       </c>
       <c r="F33" t="n">
-        <v>14.04106644619728</v>
+        <v>13.88346370324961</v>
       </c>
       <c r="G33" t="n">
-        <v>14.10490871067272</v>
+        <v>13.92844611680698</v>
       </c>
       <c r="H33" t="n">
-        <v>14.17721438198821</v>
+        <v>13.95978996974264</v>
       </c>
       <c r="I33" t="n">
-        <v>14.25204258383878</v>
+        <v>14.00757132537352</v>
       </c>
       <c r="J33" t="n">
-        <v>14.12265918538578</v>
+        <v>13.93691755181419</v>
       </c>
       <c r="K33" t="n">
-        <v>14.12090112056978</v>
+        <v>13.93131317448229</v>
       </c>
       <c r="L33" t="n">
-        <v>14.05515518469411</v>
+        <v>13.89286476588975</v>
       </c>
       <c r="M33" t="n">
-        <v>14.07719824835318</v>
+        <v>13.90202161416056</v>
       </c>
       <c r="N33" t="n">
-        <v>14.08193287692376</v>
+        <v>13.91208266340587</v>
       </c>
       <c r="O33" t="n">
-        <v>21.34291538180297</v>
+        <v>21.10138858145781</v>
       </c>
       <c r="P33" t="n">
-        <v>14.17709444379379</v>
+        <v>13.97627780129686</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.07738723406621</v>
+        <v>13.90891061444731</v>
       </c>
       <c r="R33" t="n">
-        <v>14.27607167161568</v>
+        <v>14.01981370955466</v>
       </c>
       <c r="S33" t="n">
-        <v>14.1053953566035</v>
+        <v>13.9303140776875</v>
       </c>
       <c r="T33" t="n">
-        <v>14.00707240387151</v>
+        <v>13.86360371398863</v>
       </c>
       <c r="U33" t="n">
-        <v>17.53752176612653</v>
+        <v>17.35577040346571</v>
       </c>
       <c r="V33" t="n">
-        <v>14.16426549007181</v>
+        <v>13.96503090525425</v>
       </c>
       <c r="W33" t="n">
-        <v>19.92119489320337</v>
+        <v>19.63413625005738</v>
       </c>
       <c r="X33" t="n">
-        <v>14.9173915078522</v>
+        <v>14.41669103306596</v>
       </c>
       <c r="Y33" t="n">
-        <v>14.34160722219142</v>
+        <v>14.06601116800763</v>
       </c>
       <c r="Z33" t="n">
-        <v>20.51311571296599</v>
+        <v>20.3545144367123</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.25788299787284</v>
+        <v>14.01722816267808</v>
       </c>
       <c r="AB33" t="n">
-        <v>14.07313665121228</v>
+        <v>13.89989335384225</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.72128149726636</v>
+        <v>14.41936094300508</v>
       </c>
       <c r="C33" t="n">
-        <v>8.454678766094426</v>
+        <v>8.314296393742733</v>
       </c>
       <c r="D33" t="n">
-        <v>14.66070294401506</v>
+        <v>14.36583802029394</v>
       </c>
       <c r="E33" t="n">
-        <v>11.84806045081641</v>
+        <v>11.72434771750063</v>
       </c>
       <c r="F33" t="n">
-        <v>14.60978213842024</v>
+        <v>14.334122609483</v>
       </c>
       <c r="G33" t="n">
-        <v>17.16401278100259</v>
+        <v>15.92806894039259</v>
       </c>
       <c r="H33" t="n">
-        <v>14.37649481821237</v>
+        <v>14.195780464423</v>
       </c>
       <c r="I33" t="n">
-        <v>14.57893397098335</v>
+        <v>14.31673293606885</v>
       </c>
       <c r="J33" t="n">
-        <v>15.88704583604884</v>
+        <v>15.12713764152684</v>
       </c>
       <c r="K33" t="n">
-        <v>14.75404613722228</v>
+        <v>14.42616781075453</v>
       </c>
       <c r="L33" t="n">
-        <v>14.64947977527583</v>
+        <v>14.36832662410453</v>
       </c>
       <c r="M33" t="n">
-        <v>18.50835689111867</v>
+        <v>16.67301645730458</v>
       </c>
       <c r="N33" t="n">
-        <v>14.75645315617373</v>
+        <v>14.42645212499212</v>
       </c>
       <c r="O33" t="n">
-        <v>22.18188398311295</v>
+        <v>21.86474933468032</v>
       </c>
       <c r="P33" t="n">
-        <v>15.45667129185751</v>
+        <v>14.86658381231225</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.73320042185283</v>
+        <v>14.41367511755404</v>
       </c>
       <c r="R33" t="n">
-        <v>14.44836364433649</v>
+        <v>14.23974908674815</v>
       </c>
       <c r="S33" t="n">
-        <v>14.96248329659038</v>
+        <v>14.57024145554567</v>
       </c>
       <c r="T33" t="n">
-        <v>14.50404252343311</v>
+        <v>14.27409239733866</v>
       </c>
       <c r="U33" t="n">
-        <v>18.65030526065725</v>
+        <v>18.19824398467298</v>
       </c>
       <c r="V33" t="n">
-        <v>14.55828583259075</v>
+        <v>14.31632969336824</v>
       </c>
       <c r="W33" t="n">
-        <v>20.81886674996217</v>
+        <v>20.35215978856165</v>
       </c>
       <c r="X33" t="n">
-        <v>15.02315297986144</v>
+        <v>14.58014264054806</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.23713570433556</v>
+        <v>14.71590580496181</v>
       </c>
       <c r="Z33" t="n">
-        <v>21.5535356878452</v>
+        <v>21.14871369607224</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.7814987005478</v>
+        <v>14.44403300689091</v>
       </c>
       <c r="AB33" t="n">
-        <v>18.4206087177755</v>
+        <v>16.51152581567008</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14.44311865273631</v>
+        <v>14.19952219146081</v>
       </c>
       <c r="C33" t="n">
-        <v>8.362131481906772</v>
+        <v>8.212918027813085</v>
       </c>
       <c r="D33" t="n">
-        <v>14.20672268712864</v>
+        <v>14.04697677856601</v>
       </c>
       <c r="E33" t="n">
-        <v>11.6390768392082</v>
+        <v>11.55744372185485</v>
       </c>
       <c r="F33" t="n">
-        <v>14.16066500141778</v>
+        <v>14.01871692866352</v>
       </c>
       <c r="G33" t="n">
-        <v>16.35284478724287</v>
+        <v>15.39774056307652</v>
       </c>
       <c r="H33" t="n">
-        <v>14.26858803567783</v>
+        <v>14.08031787293126</v>
       </c>
       <c r="I33" t="n">
-        <v>14.28748093008998</v>
+        <v>14.09437404427065</v>
       </c>
       <c r="J33" t="n">
-        <v>14.99317907459791</v>
+        <v>14.53973811270939</v>
       </c>
       <c r="K33" t="n">
-        <v>14.394515265471</v>
+        <v>14.15846254111532</v>
       </c>
       <c r="L33" t="n">
-        <v>14.33795860803973</v>
+        <v>14.12934077060321</v>
       </c>
       <c r="M33" t="n">
-        <v>14.61580559869739</v>
+        <v>14.28868947524266</v>
       </c>
       <c r="N33" t="n">
-        <v>14.3822153625689</v>
+        <v>14.15388956501553</v>
       </c>
       <c r="O33" t="n">
-        <v>21.61341636313442</v>
+        <v>21.39389950458684</v>
       </c>
       <c r="P33" t="n">
-        <v>14.77101074682075</v>
+        <v>14.40223488319046</v>
       </c>
       <c r="Q33" t="n">
-        <v>14.47120662745381</v>
+        <v>14.21091395167951</v>
       </c>
       <c r="R33" t="n">
-        <v>14.27271727085658</v>
+        <v>14.08475722739736</v>
       </c>
       <c r="S33" t="n">
-        <v>14.3307352493987</v>
+        <v>14.1299455991575</v>
       </c>
       <c r="T33" t="n">
-        <v>14.17203258622434</v>
+        <v>14.02716561932171</v>
       </c>
       <c r="U33" t="n">
-        <v>17.89072032990524</v>
+        <v>17.66675894305586</v>
       </c>
       <c r="V33" t="n">
-        <v>14.33649303291224</v>
+        <v>14.13108158066133</v>
       </c>
       <c r="W33" t="n">
-        <v>20.36139713385791</v>
+        <v>20.00128722814731</v>
       </c>
       <c r="X33" t="n">
-        <v>14.89417535910716</v>
+        <v>14.4570348816545</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.679213132959</v>
+        <v>14.92815437188448</v>
       </c>
       <c r="Z33" t="n">
-        <v>20.8312078122975</v>
+        <v>20.62036948651147</v>
       </c>
       <c r="AA33" t="n">
-        <v>14.31816343409093</v>
+        <v>14.11757500139568</v>
       </c>
       <c r="AB33" t="n">
-        <v>16.5783502192991</v>
+        <v>15.41517138427791</v>
       </c>
     </row>
   </sheetData>
